--- a/Product_Commercial_Tracker.xlsx
+++ b/Product_Commercial_Tracker.xlsx
@@ -638,12 +638,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Confirm folder location &amp; that Product will keep it updated</t>
+          <t>Jason to commit Product team to keep it updated</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Kelly coordinates access; Product owns content</t>
+          <t>Kelly has folder access; Jason committing Product team to maintain content</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Agree owner at next meeting</t>
+          <t>Assign an owner at Session 3</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Identified gap — no owner yet</t>
+          <t>Identified gap — no owner yet. TBD (not Kelly)</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Agree owner &amp; format (visual + commentary)</t>
+          <t>Assign an owner at Session 3; agree format</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Identified gap; possible AI-assisted approach</t>
+          <t>Identified gap; possible AI-assisted approach. TBD (not Kelly)</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Share this workbook + structure doc</t>
+          <t>Share workbook + structure doc; sign-off from Feron &amp; Jason</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Kelly's deliverable</t>
+          <t>Kelly's deliverable; leads = Feron (commercial) &amp; Jason (product)</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Two identified gaps with no owner</t>
+          <t>Two identified gaps with no owner (not Kelly)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Agree owners at Session 3</t>
+          <t>Session 3 agenda item: assign an owner</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">

--- a/Product_Commercial_Tracker.xlsx
+++ b/Product_Commercial_Tracker.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Stephen pushing to Stake</t>
+          <t>Steven pushing to Stake</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">

--- a/Product_Commercial_Tracker.xlsx
+++ b/Product_Commercial_Tracker.xlsx
@@ -66,12 +66,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="00111111"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E5496"/>
+        <fgColor rgb="000B5D2E"/>
       </patternFill>
     </fill>
     <fill>

--- a/Product_Commercial_Tracker.xlsx
+++ b/Product_Commercial_Tracker.xlsx
@@ -488,18 +488,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -519,45 +518,40 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Action / Topic</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Action / Topic</t>
+          <t>Raised in Meeting</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Raised in Meeting</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Next Step</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Next Step</t>
+          <t>Target / Due</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Target / Due</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -566,45 +560,40 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>EXAMPLE — Confirm Q3 Plinko release date with Product</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>EXAMPLE — Confirm Q3 Plinko release date with Product</t>
+          <t>Sep 2026 (Session 2)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Sep 2026 (Session 2)</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Product to confirm target quarter</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Product to confirm target quarter</t>
+          <t>Next meeting</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Next meeting</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Example row — delete before use</t>
         </is>
@@ -613,92 +602,82 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Product roadmap accessible via Global Product SharePoint folder (status + target dates)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Product roadmap accessible via Global Product SharePoint folder (status + target dates)</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Facilitator</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Jason to commit Product team to keep it updated</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Jason to commit Product team to keep it updated</t>
+          <t>Before Sess. 3</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Before Sess. 3</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Kelly has folder access; Jason committing Product team to maintain content</t>
+          <t>Facilitator has folder access; Jason committing Product team to maintain content</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>Establish action/roadmap follow-up so each meeting reviews prior items</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Establish action/roadmap follow-up so each meeting reviews prior items</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Facilitator</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Stand up this tracker + share with group</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Stand up this tracker + share with group</t>
+          <t>Before Sess. 3</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Before Sess. 3</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>This workbook</t>
         </is>
@@ -707,92 +686,82 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>Share product demos/visuals so Commercial can prepare (e.g. cricket roulette demo from Josh)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Share product demos/visuals so Commercial can prepare (e.g. cricket roulette demo from Josh)</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Product to circulate available demos</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Product to circulate available demos</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Josh has cricket roulette demo; Kelly to request</t>
+          <t>Josh has cricket roulette demo</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>Astro → Betman integration plan</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Astro → Betman integration plan</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Confirm approach &amp; rough timing</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Product to confirm approach &amp; rough timing</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Jason flagged as a specific requirement</t>
         </is>
@@ -801,45 +770,40 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>Third-party games — strategic review + business case (continue or not, outside Aviator)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Third-party games — strategic review + business case (continue or not, outside Aviator)</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Review Paul's earlier analysis; commercial to build case</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Review Paul's earlier analysis; commercial to build case</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Needs decision + possible dedicated resource</t>
         </is>
@@ -848,45 +812,40 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>Mobile POS / retail opportunity — commercial validation before final decision</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Mobile POS / retail opportunity — commercial validation before final decision</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Retail team</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Retail team</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Retail (Dieg/Tony/Tom) to finalise business case w/ data</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Retail (Dieg/Tony/Tom) to finalise business case w/ data</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>East Africa / Golden Race competitive pressure</t>
         </is>
@@ -895,139 +854,124 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>Competitive product analysis (our products vs competitors) — agree owner &amp; scope</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Competitive product analysis (our products vs competitors) — agree owner &amp; scope</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Assign an owner at Session 3</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Assign an owner at Session 3</t>
+          <t>Sess. 3</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Sess. 3</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Identified gap — no owner yet. TBD (not Kelly)</t>
+          <t>Identified gap — no owner yet. TBD (not Facilitator)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>Insight-driven product performance view (narrative, not just Power BI)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Insight-driven product performance view (narrative, not just Power BI)</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Assign an owner at Session 3; agree format</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Assign an owner at Session 3; agree format</t>
+          <t>Sess. 3</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Sess. 3</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Identified gap; possible AI-assisted approach. TBD (not Kelly)</t>
+          <t>Identified gap; possible AI-assisted approach. TBD (not Facilitator)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>Link GTM / customer comms more closely to upcoming releases</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Link GTM / customer comms more closely to upcoming releases</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Feed into Patrick's GTM board</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Feed into Patrick's GTM board</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Philip/Josh/Jade → Patrick's board</t>
         </is>
@@ -1036,45 +980,40 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>Share recent football / cinematic updates with team + marketing</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Share recent football / cinematic updates with team + marketing</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Product to send footage; confirm in marketing assets</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Product to send footage; confirm in marketing assets</t>
+          <t>Before Sess. 3</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>Before Sess. 3</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Sarah requested; Jason has video</t>
         </is>
@@ -1083,92 +1022,82 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>Propose meeting structure / action-tracking to group for input</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Propose meeting structure / action-tracking to group for input</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Facilitator</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Share workbook + structure doc; sign-off from Feron &amp; Jason</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Share workbook + structure doc; sign-off from Feron &amp; Jason</t>
+          <t>Before Sess. 3</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Before Sess. 3</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Kelly's deliverable; leads = Feron (commercial) &amp; Jason (product)</t>
+          <t>Leads = Feron (commercial) &amp; Jason (product)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>Schedule next monthly session (proposed 18 Sep, 11:00–12:00)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Schedule next monthly session (proposed 18 Sep, 11:00–12:00)</t>
+          <t>Session 2</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Facilitator</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Confirm availability, send invite</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Confirm availability, send invite</t>
+          <t>18 Sep</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Awaiting confirmations</t>
         </is>
@@ -1176,17 +1105,17 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="3">
+    <dataValidation sqref="C4:C57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Facilitator,Product,Commercial,Marketing,Retail team,TBD"</formula1>
+    </dataValidation>
     <dataValidation sqref="D4:D57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Kelly,Product,Commercial,Marketing,Retail team,TBD"</formula1>
+      <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"High,Medium,Low"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In Progress,Blocked,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1200,18 +1129,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1231,45 +1159,40 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Product / Feature</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Product / Feature</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Stage</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Target Release</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Target Release</t>
+          <t>Commercial Angle</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Commercial Angle</t>
+          <t>Status Change</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Status Change</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Updated</t>
         </is>
@@ -1278,45 +1201,40 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>VSE</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VSE</t>
+          <t>EXAMPLE — New race track pack</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>EXAMPLE — New race track pack</t>
+          <t>Additional dirt/turf tracks for Betmakers global launch</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Additional dirt/turf tracks for Betmakers global launch</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Q4 2026</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Q4 2026</t>
+          <t>Variety for global distribution</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Variety for global distribution</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
@@ -1325,45 +1243,40 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>VSE</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>VSE</t>
+          <t>One-minute horse racing (sprint)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>One-minute horse racing (sprint)</t>
+          <t>Shorter event envelope following Entain success; English-look sprint product</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Shorter event envelope following Entain success; English-look sprint product</t>
+          <t>In Dev</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>ASAP</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>ASAP</t>
+          <t>Match Entain need; roll across all online racing</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Match Entain need; roll across all online racing</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1372,45 +1285,40 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>VSE</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>VSE</t>
+          <t>Sprint dog racing</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Sprint dog racing</t>
+          <t>Switch dog racing to shorter single-loop format</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Switch dog racing to shorter single-loop format</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Consistency with sprint racing</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Consistency with sprint racing</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1419,45 +1327,40 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>VSE</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>VSE</t>
+          <t>Faster football (1-min envelope)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Faster football (1-min envelope)</t>
+          <t>6-goal game completing within one minute</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>6-goal game completing within one minute</t>
+          <t>In Dev</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1-min game intervals online</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>1-min game intervals online</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1466,45 +1369,40 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>VSE</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>VSE</t>
+          <t>New race tracks (variety)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>New race tracks (variety)</t>
+          <t>6–8 tracks incl. more dirt for US/global</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>6–8 tracks incl. more dirt for US/global</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Post-Betmakers</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Post-Betmakers</t>
+          <t>Needed for Betmakers global deal</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Needed for Betmakers global deal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1513,45 +1411,40 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>VSE</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>VSE</t>
+          <t>Racing visuals refresh</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Racing visuals refresh</t>
+          <t>Modernised preamble/results, more energetic horse animation</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Modernised preamble/results, more energetic horse animation</t>
+          <t>In Dev</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>With sprint</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>With sprint</t>
+          <t>Refresh vs 2015-era look</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Refresh vs 2015-era look</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1560,45 +1453,40 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Italian 3-goal micro-betting football</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Italian 3-goal micro-betting football</t>
+          <t>Header/penalty/L-R foot/save micro events</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Header/penalty/L-R foot/save micro events</t>
+          <t>In Dev</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Italian operators keen</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Italian operators keen</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1607,45 +1495,40 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>iGoal / Bet Power</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>iGoal / Bet Power</t>
+          <t>Sustained-revenue instant football; strong margin</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Sustained-revenue instant football; strong margin</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Retains revenue vs slots</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Retains revenue vs slots</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1654,45 +1537,40 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>'Hop' — new math game</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>'Hop' — new math game</t>
+          <t>Original simple math-based instant game</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Original simple math-based instant game</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>After racing</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>After racing</t>
+          <t>New original IP</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>New original IP</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1701,45 +1579,40 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Cricket roulette</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Cricket roulette</t>
+          <t>Demo available (Josh) — target Stake</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Demo available (Josh) — target Stake</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Steven pushing to Stake</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Steven pushing to Stake</t>
+          <t>Demo ready</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Demo ready</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1748,45 +1621,40 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>Betman</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Betman</t>
+          <t>Mobile / retail wallet</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Mobile / retail wallet</t>
+          <t>Voucher-based play across terminals &amp; mobile in-venue</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Voucher-based play across terminals &amp; mobile in-venue</t>
+          <t>Staging</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Staging</t>
+          <t>Post v6</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Post v6</t>
+          <t>Transformative for African retail</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Transformative for African retail</t>
+          <t>New release</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>New release</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1795,45 +1663,40 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>Betman</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Betman</t>
+          <t>Vision X + Net4Media (racing)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Vision X + Net4Media (racing)</t>
+          <t>Horse then dog racing on Net4Media to cut bandwidth</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Horse then dog racing on Net4Media to cut bandwidth</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Bandwidth-light shop content</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Bandwidth-light shop content</t>
+          <t>Next up</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Next up</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1842,45 +1705,40 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>Betman</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Betman</t>
+          <t>Football cinematic close-ups</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Football cinematic close-ups</t>
+          <t>New close-up/replay sequences; multilingual soccer</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>New close-up/replay sequences; multilingual soccer</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Marketing asset for customers</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Marketing asset for customers</t>
+          <t>Recently shipped</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Recently shipped</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -1888,14 +1746,14 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B4:B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A4:A57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VSE,Instant,Betman,Cross"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4:D57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Concept,In Dev,Staging,Production,Parked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1909,19 +1767,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1934,57 +1791,52 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HOW TO USE:  Commercial logs what customers/markets are asking for. Link to a Product Roadmap ID where relevant. This is the 'two-way' input the meeting is built around.</t>
+          <t>HOW TO USE:  Commercial logs what customers/markets are asking for. Name the linked roadmap item so the connection holds. This is the 'two-way' input the meeting is built around.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Date Raised</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Date Raised</t>
+          <t>Customer / Market</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Customer / Market</t>
+          <t>Tier</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>Request / Feedback</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Request / Feedback</t>
+          <t>Product Area</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Product Area</t>
+          <t>Linked Roadmap Item</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Linked Roadmap ID</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1993,50 +1845,45 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>01 Sep 26</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>01 Sep 26</t>
+          <t>Betway (SA)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Betway (SA)</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>EXAMPLE — Interested in Plinko-style game</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>EXAMPLE — Interested in Plinko-style game</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>→ (name the roadmap item)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Example row — delete before use</t>
         </is>
@@ -2045,50 +1892,45 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>Sep 26</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Third-party game clients</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Third-party game clients</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Want newest Astro / ESA / other third-party games distributed</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Want newest Astro / ESA / other third-party games distributed</t>
+          <t>Betman</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Betman</t>
+          <t>→ Astro → Betman integration</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>P-Astro</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Blocked on Betman integration</t>
         </is>
@@ -2097,102 +1939,92 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>Sep 26</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Ethiopia market</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Ethiopia market</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>Market entry — third-party (Galaxis/Smartsoft/Split the Pot) interest</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Market entry — third-party (Galaxis/Smartsoft/Split the Pot) interest</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Parked</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Prove payment first (Jason) before more games</t>
+          <t>Prove payment first before more games</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>Sep 26</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>Italian operators</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Italian operators</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Keen on 3-goal micro-betting football</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Keen on 3-goal micro-betting football</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>→ Italian 3-goal micro-betting football</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Salivating per Jason</t>
         </is>
@@ -2201,50 +2033,45 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>Sep 26</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Sep 26</t>
+          <t>East Africa retail</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>East Africa retail</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Retail solution to counter Golden Race</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Retail solution to counter Golden Race</t>
+          <t>Betman</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Betman</t>
+          <t>→ Mobile POS / retail opportunity</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Retail team</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Retail team</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Mobile POS business case</t>
         </is>
@@ -2252,21 +2079,21 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D4:D49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C4:C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Tier 1,Tier 2,Tier 3,—"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VSE,Instant,Betman,Cross"</formula1>
     </dataValidation>
-    <dataValidation sqref="H4:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G4:G49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In Progress,Blocked,Done,Parked"</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Kelly,Product,Commercial,Marketing,Retail team,TBD"</formula1>
+    <dataValidation sqref="H4:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Facilitator,Product,Commercial,Marketing,Retail team,TBD"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2279,17 +2106,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2309,40 +2135,35 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Detail</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Detail</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Decision / Answer</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Decision / Answer</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
@@ -2351,40 +2172,35 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>EXAMPLE — Continue third-party slots?</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>EXAMPLE — Continue third-party slots?</t>
+          <t>Whether to endure beyond proof-of-concept</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Whether to endure beyond proof-of-concept</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Pending business case</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Pending business case</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
@@ -2393,40 +2209,35 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Do we continue third-party games (outside Aviator)?</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Do we continue third-party games (outside Aviator)?</t>
+          <t>Thin margins; needs dedicated resource + channel</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Thin margins; needs dedicated resource + channel</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Awaiting business case &amp; commercial decision</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Awaiting business case &amp; commercial decision</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -2435,40 +2246,35 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Do we stay in East Africa retail?</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Do we stay in East Africa retail?</t>
+          <t>Golden Race pressure; mobile POS viability</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Golden Race pressure; mobile POS viability</t>
+          <t>Retail team</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Retail team</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Needs data-backed argument</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Needs data-backed argument</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -2477,40 +2283,35 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Who owns competitive analysis + product-performance narrative?</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Who owns competitive analysis + product-performance narrative?</t>
+          <t>Two identified gaps with no owner (not Facilitator)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Two identified gaps with no owner (not Kelly)</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Session 3 agenda item: assign an owner</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Session 3 agenda item: assign an owner</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -2519,40 +2320,35 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Move to one-minute racing events</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Move to one-minute racing events</t>
+          <t>Testing on Betman OK; move ahead</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Testing on Betman OK; move ahead</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Proceeding — sprint format</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Proceeding — sprint format</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -2561,40 +2357,35 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Cancel full CG racing revamp</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Cancel full CG racing revamp</t>
+          <t>Poor results vs cost</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Poor results vs cost</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Cancelled; refine current instead</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Cancelled; refine current instead</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -2603,40 +2394,35 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Ethiopia: prove payment before more games</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Ethiopia: prove payment before more games</t>
+          <t>Sequence risk down</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Sequence risk down</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Go live w/ existing, 1 month, then expand</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Go live w/ existing, 1 month, then expand</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -2644,17 +2430,17 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="B4:B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A4:A51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Decision,Question"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Kelly,Product,Commercial,Marketing,Retail team,TBD"</formula1>
+    <dataValidation sqref="D4:D51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Facilitator,Product,Commercial,Marketing,Retail team,TBD"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In Progress,Blocked,Done,Parked"</formula1>
     </dataValidation>
   </dataValidations>
